--- a/artfynd/A 44797-2025 artfynd.xlsx
+++ b/artfynd/A 44797-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75247428</v>
+        <v>75247427</v>
       </c>
       <c r="B2" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brändtlandet, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602778.0238948787</v>
+        <v>602778</v>
       </c>
       <c r="R2" t="n">
-        <v>7070963.175265309</v>
+        <v>7070963</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,21 +743,11 @@
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -783,12 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>drygt 100-årig renbetad tallskog med gamla tallöverståndare, på morän</t>
-        </is>
+          <t>gammal, skiktad tallnaturskog på moränudde ut mot myr</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>bland tunn väggmossa, ljung och lingon</t>
+          <t>1 substratenheter # grov gammal tallåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,42 +789,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75247432</v>
+        <v>75247429</v>
       </c>
       <c r="B3" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602761.1654230163</v>
+        <v>602778</v>
       </c>
       <c r="R3" t="n">
-        <v>7071072.043895594</v>
+        <v>7070963</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,21 +866,11 @@
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -923,7 +887,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>bland väggmossa och lingon vid stig</t>
+          <t>bland väggmossa, ljung och lingon</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,19 +909,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75247429</v>
+        <v>75247430</v>
       </c>
       <c r="B4" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -994,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602778.0238948787</v>
+        <v>602751</v>
       </c>
       <c r="R4" t="n">
-        <v>7070963.175265309</v>
+        <v>7071070</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1027,21 +986,11 @@
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1058,7 +1007,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>bland väggmossa, ljung och lingon</t>
+          <t>bland väggmossa och lingon vid stig</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1083,12 +1032,7 @@
         <v>75247431</v>
       </c>
       <c r="B5" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602751.0319692836</v>
+        <v>602751</v>
       </c>
       <c r="R5" t="n">
-        <v>7071069.941452986</v>
+        <v>7071070</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1162,19 +1106,9 @@
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,15 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>75247430</v>
+        <v>75247432</v>
       </c>
       <c r="B6" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,26 +1160,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602751.0319692836</v>
+        <v>602761</v>
       </c>
       <c r="R6" t="n">
-        <v>7071069.941452986</v>
+        <v>7071072</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1297,19 +1226,9 @@
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,50 +1269,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>75247427</v>
+        <v>75247428</v>
       </c>
       <c r="B7" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brändtlandet, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602778.0238948787</v>
+        <v>602778</v>
       </c>
       <c r="R7" t="n">
-        <v>7070963.175265309</v>
+        <v>7070963</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1423,21 +1346,11 @@
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1449,15 +1362,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>gammal, skiktad tallnaturskog på moränudde ut mot myr</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
+          <t>drygt 100-årig renbetad tallskog med gamla tallöverståndare, på morän</t>
+        </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal tallåga</t>
+          <t>bland tunn väggmossa, ljung och lingon</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1472,6 +1382,120 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>75247434</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brändtlandet, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>602921</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7071110</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>drygt 100-årig, ogallrad tallskog, på morän</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>2 substratenheter # brandhögstubbar</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 44797-2025 artfynd.xlsx
+++ b/artfynd/A 44797-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247427</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247429</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247430</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247431</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1266,6 +1291,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247432</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1386,6 +1416,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247428</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,8 +1535,22 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247434</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>